--- a/artfynd/A 25558-2019 artfynd.xlsx
+++ b/artfynd/A 25558-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125160535</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25558-2019 artfynd.xlsx
+++ b/artfynd/A 25558-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125160535</v>
       </c>
       <c r="B2" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
